--- a/data/weekly_data_clean/input/产品表现父ASIN-26W18.xlsx
+++ b/data/weekly_data_clean/input/产品表现父ASIN-26W18.xlsx
@@ -380,10 +380,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="13" width="20.7109375" style="2" customWidth="1"/>
+    <col min="1" max="14" width="20.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -399,55 +399,60 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>品名</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>销量</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>销售额</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>订单量</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sessions-Browser</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Sessions-Mobile</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Sessions-Total</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>PV-Browser</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>PV-Mobile</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>PV-Total</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>CVR</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>TACOS</t>
         </is>
@@ -460,13 +465,11 @@
         </is>
       </c>
       <c r="B2" s="2"/>
-      <c r="C2" s="3">
-        <v>0</v>
-      </c>
-      <c r="D2" s="4">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="C2" s="2"/>
+      <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
         <v>0</v>
       </c>
       <c r="F2" s="3">
@@ -487,12 +490,15 @@
       <c r="K2" s="3">
         <v>0</v>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+      <c r="L2" s="3">
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
@@ -505,13 +511,11 @@
         </is>
       </c>
       <c r="B3" s="2"/>
-      <c r="C3" s="3">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3">
+      <c r="C3" s="2"/>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
         <v>0</v>
       </c>
       <c r="F3" s="3">
@@ -532,12 +536,15 @@
       <c r="K3" s="3">
         <v>0</v>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+      <c r="L3" s="3">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
@@ -550,39 +557,40 @@
         </is>
       </c>
       <c r="B4" s="2"/>
-      <c r="C4" s="3">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="C4" s="2"/>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
         <v>0</v>
       </c>
       <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
         <v>3</v>
       </c>
-      <c r="G4" s="3">
+      <c r="H4" s="3">
         <v>1</v>
       </c>
-      <c r="H4" s="3">
+      <c r="I4" s="3">
         <v>4</v>
       </c>
-      <c r="I4" s="3">
+      <c r="J4" s="3">
         <v>3</v>
       </c>
-      <c r="J4" s="3">
+      <c r="K4" s="3">
         <v>1</v>
       </c>
-      <c r="K4" s="3">
+      <c r="L4" s="3">
         <v>4</v>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
       <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
@@ -595,13 +603,11 @@
         </is>
       </c>
       <c r="B5" s="2"/>
-      <c r="C5" s="3">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3">
+      <c r="C5" s="2"/>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
         <v>0</v>
       </c>
       <c r="F5" s="3">
@@ -622,12 +628,15 @@
       <c r="K5" s="3">
         <v>0</v>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+      <c r="L5" s="3">
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
@@ -640,13 +649,11 @@
         </is>
       </c>
       <c r="B6" s="2"/>
-      <c r="C6" s="3">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3">
+      <c r="C6" s="2"/>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
         <v>0</v>
       </c>
       <c r="F6" s="3">
@@ -667,12 +674,15 @@
       <c r="K6" s="3">
         <v>0</v>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+      <c r="L6" s="3">
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
@@ -685,13 +695,11 @@
         </is>
       </c>
       <c r="B7" s="2"/>
-      <c r="C7" s="3">
-        <v>0</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3">
+      <c r="C7" s="2"/>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
         <v>0</v>
       </c>
       <c r="F7" s="3">
@@ -712,12 +720,15 @@
       <c r="K7" s="3">
         <v>0</v>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+      <c r="L7" s="3">
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
@@ -729,40 +740,49 @@
           <t>B0DFYL28MK</t>
         </is>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="3">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>ToyDH</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>ToyDH MintGreen 1Pack,ToyDH Black 1Pack,ToyDH Green 1Pack,ToyDH Pink 1Pack,ToyDH Black 2Pack,ToyDH Orange 1Pack,ToyDH Yellow 1Pack,ToyDH Green 2Pack,ToyDH MintGreen 2Pack,ToyDH Orange 2Pack,ToyDH Pink 2Pack,ToyDH Yellow 2Pack</t>
+        </is>
+      </c>
+      <c r="D8" s="3">
         <v>19</v>
       </c>
-      <c r="D8" s="4">
+      <c r="E8" s="4">
         <v>405.02</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>18</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>37</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>106</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>143</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>46</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>127</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>173</v>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>12.59%</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>10.76%</t>
         </is>
@@ -774,40 +794,49 @@
           <t>B0DFYLW9ZZ</t>
         </is>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="3">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>ShortDL</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>ShortL Greem 1.2FT,ShortL MintGreen 1.2FT,ShortL Black 1.2FT,ShortL Orange 1.2FT,ShortL Pink 1.2FT,ShortL Yellow 1.2FT</t>
+        </is>
+      </c>
+      <c r="D9" s="3">
         <v>2</v>
       </c>
-      <c r="D9" s="4">
+      <c r="E9" s="4">
         <v>29.98</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>23</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>48</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>71</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>32</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>57</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>89</v>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>2.82%</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>20.91%</t>
         </is>
@@ -820,39 +849,44 @@
         </is>
       </c>
       <c r="B10" s="2"/>
-      <c r="C10" s="3">
-        <v>0</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>WB Black 21oz,WB Green 21oz,WB MintGreen 21oz,WB Red 21oz,WB White 21oz,WB Yellow 21oz</t>
+        </is>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4">
         <v>0</v>
       </c>
       <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
         <v>5</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6</v>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
       <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
@@ -865,39 +899,40 @@
         </is>
       </c>
       <c r="B11" s="2"/>
-      <c r="C11" s="3">
+      <c r="C11" s="2"/>
+      <c r="D11" s="3">
         <v>1</v>
       </c>
-      <c r="D11" s="4">
+      <c r="E11" s="4">
         <v>27.99</v>
       </c>
-      <c r="E11" s="3">
+      <c r="F11" s="3">
         <v>1</v>
       </c>
-      <c r="F11" s="3">
+      <c r="G11" s="3">
         <v>6</v>
       </c>
-      <c r="G11" s="3">
+      <c r="H11" s="3">
         <v>10</v>
       </c>
-      <c r="H11" s="3">
+      <c r="I11" s="3">
         <v>16</v>
       </c>
-      <c r="I11" s="3">
+      <c r="J11" s="3">
         <v>9</v>
       </c>
-      <c r="J11" s="3">
+      <c r="K11" s="3">
         <v>11</v>
       </c>
-      <c r="K11" s="3">
+      <c r="L11" s="3">
         <v>20</v>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>6.25%</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>2.43%</t>
         </is>
@@ -909,40 +944,49 @@
           <t>B0DPLCKLZK</t>
         </is>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="3">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>DSL</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>DSL Black 6FT,DSL MultiColor 6FT,DSL MultiColor 3FT,DSL Orange 6FT,DSL Black 3FT,DSL Green 6FT,DSL MintGreen 3FT,DSL Orange 3FT,DSL Red 3FT,DSL Red 6FT,DSL Green 3FT,DSL MintGreen 6FT</t>
+        </is>
+      </c>
+      <c r="D12" s="3">
         <v>33</v>
       </c>
-      <c r="D12" s="4">
+      <c r="E12" s="4">
         <v>864.4299999999999</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>32</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>159</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>377</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>536</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>246</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>441</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>687</v>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>5.97%</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>27.41%</t>
         </is>
@@ -954,40 +998,49 @@
           <t>B0F8HHZ2CB</t>
         </is>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="3">
-        <v>0</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SFM</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>SFM 1 Blue,SFM 1 Red,SFM 1 Yellow,SFM 2 BlueRed,SFM 2 BlueYellow,SFM 3 BlueYellowRed</t>
+        </is>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4">
         <v>0</v>
       </c>
       <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
         <v>12</v>
       </c>
-      <c r="G13" s="3">
+      <c r="H13" s="3">
         <v>17</v>
       </c>
-      <c r="H13" s="3">
+      <c r="I13" s="3">
         <v>29</v>
       </c>
-      <c r="I13" s="3">
+      <c r="J13" s="3">
         <v>16</v>
       </c>
-      <c r="J13" s="3">
+      <c r="K13" s="3">
         <v>20</v>
       </c>
-      <c r="K13" s="3">
+      <c r="L13" s="3">
         <v>36</v>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
       <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>100.00%</t>
         </is>
@@ -1004,39 +1057,44 @@
           <t>Toy</t>
         </is>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Toy Black Short w/oBall 1Pack,Toy Purple Long w/oBall 1Pack,Toy Black w/Ball 1Pack,Toy Black Long w/oBall 1Pack,Toy Orange Long w/oBall 1Pack,Toy Green Short w/oBall 1Pack,Toy Orange w/Ball 1Pack,Toy Purple w/Ball 1Pack,Toy Purple Short w/oBall 1Pack,Toy Green w/Ball 1Pack,Toy Orange Short w/oBall 1Pack,Toy Black Long w/oBall 2Pack,Toy Green Long w/oBall 1Pack,Toy Green Long w/oBall 2Pack,Toy Orange Long w/oBall 2Pack,Toy Purple Long w/oBall 2Pack</t>
+        </is>
+      </c>
+      <c r="D14" s="3">
         <v>68</v>
       </c>
-      <c r="D14" s="4">
+      <c r="E14" s="4">
         <v>1500.45</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>67</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>231</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>831</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>271</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>679</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>950</v>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>8.06%</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>20.39%</t>
         </is>
@@ -1048,40 +1106,49 @@
           <t>B0GR928XD8</t>
         </is>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="3">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>SL Black 5.5FT,SL Black 5.0FT,SL Black 3.6FT,SL Green 5.5FT,SL Green 5.0FT,SL MultiColor 5.5FT,SL Brown 5.5FT,SL Lavender 5.0FT,SL Green 3.6FT,SL MintGreen 5.5FT,SL Lavender 5.5FT,SL Pink 5.5FT,SL MultiColor 5.0FT,SL Pink 3.6FT,SL Red 5.5FT,SL Orange 3.6FT,SL MultiColor 3.6FT,SL Red 3.6FT,SL Orange 5.0FT,SL MintGreen 5.0FT,SL Red 5.0FT,SL Brown 5.0FT,SL Pink 5.0FT,SL Lavender 3.6FT,SL Orange 5.5FT,SL Brown 3.6FT,SL MintGreen 3.6FT,SL Blue 5.0FT,SL Gray 5.0FT,SL Purple 5.0FT,SL Blue 3.6FT,SL Gray 3.6FT,SL Purple 3.6FT</t>
+        </is>
+      </c>
+      <c r="D15" s="3">
         <v>531</v>
       </c>
-      <c r="D15" s="4">
+      <c r="E15" s="4">
         <v>11609.97</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>507</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1306</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4876</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>6182</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1698</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>6112</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>7810</v>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>8.20%</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>23.85%</t>
         </is>
@@ -1093,40 +1160,49 @@
           <t>B0GVYMDJ1V</t>
         </is>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="3">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>MFL</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>MFL Yellow AL,MFL Black AL,MFL Green AL,MFL MintGreen AL,MFL MintGreen ZN,MFL Black ZN,MFL Green ZN,MFL Red AL,MFL Red ZN,MFL Yellow ZN</t>
+        </is>
+      </c>
+      <c r="D16" s="3">
         <v>13</v>
       </c>
-      <c r="D16" s="4">
+      <c r="E16" s="4">
         <v>295.83</v>
       </c>
-      <c r="E16" s="3">
+      <c r="F16" s="3">
         <v>13</v>
       </c>
-      <c r="F16" s="3">
+      <c r="G16" s="3">
         <v>81</v>
       </c>
-      <c r="G16" s="3">
+      <c r="H16" s="3">
         <v>293</v>
       </c>
-      <c r="H16" s="3">
+      <c r="I16" s="3">
         <v>374</v>
       </c>
-      <c r="I16" s="3">
+      <c r="J16" s="3">
         <v>100</v>
       </c>
-      <c r="J16" s="3">
+      <c r="K16" s="3">
         <v>394</v>
       </c>
-      <c r="K16" s="3">
+      <c r="L16" s="3">
         <v>494</v>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>3.48%</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>27.78%</t>
         </is>
@@ -1139,13 +1215,15 @@
         </is>
       </c>
       <c r="B17" s="2"/>
-      <c r="C17" s="3">
-        <v>0</v>
-      </c>
-      <c r="D17" s="4">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>SC Black,SC Brown,SC MultiColor,SC Pink,SC Green,SC Lavender,SC MintGreen,SC Orange,SC Red</t>
+        </is>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4">
         <v>0</v>
       </c>
       <c r="F17" s="3">
@@ -1166,12 +1244,15 @@
       <c r="K17" s="3">
         <v>0</v>
       </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+      <c r="L17" s="3">
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
@@ -1183,40 +1264,49 @@
           <t>B0GX1CWP8Y</t>
         </is>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="3">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>DL</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>DL Black w/oHandle AL 2.0,DL Pink w/oHandle ZN 2.0,DL Black w/oHandle AL 1.5,DL Brown w/oHandle AL 1.5,DL Orange w/oHandle ZN 2.0,DL Orange w/oHandle AL 2.0,DL MintGreen w/oHandle AL 2.0,DL Brown w/oHandle AL 2.0,DL Brown w/oHandle ZN 2.0,DL Green w/oHandle AL 2.0,DL Green w/oHandle ZN 2.0,DL Pink w/oHandle AL 2.0,DL Lavender w/oHandle ZN 2.0,DL MintGreen w/oHandle AL 1.5,DL Orange w/oHandle AL 1.5,DL Pink w/oHandle AL 1.5,DL Black w/oHandle ZN 2.0,DL Green w/oHandle AL 1.5,DL Lavender w/oHandle AL 1.5,DL Lavender w/oHandle AL 2.0,DL MintGreen w/oHandle ZN 2.0,DL Yellow w/oHandle AL 1.5,DL Yellow w/oHandle ZN 2.0,DL Yellow w/oHandle AL 2.0</t>
+        </is>
+      </c>
+      <c r="D18" s="3">
         <v>32</v>
       </c>
-      <c r="D18" s="4">
+      <c r="E18" s="4">
         <v>649.74</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>28</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>127</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>355</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>482</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>164</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>417</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>581</v>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>5.81%</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>30.94%</t>
         </is>
@@ -1228,40 +1318,49 @@
           <t>B0GX1N8TMK</t>
         </is>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="3">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>DL</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>DL Black w/Handle ZN 2.0,DL Black w/Handle AL 1.5,DL Black w/Handle AL 2.0,DL MintGreen w/Handle AL 1.5,DL Green w/Handle ZN 2.0,DL Pink w/Handle ZN 2.0,DL Lavender w/Handle AL 1.5,DL Green w/Handle AL 1.5,DL Orange w/Handle AL 2.0,DL MintGreen w/Handle AL 2.0,DL Pink w/Handle AL 1.5,DL Yellow w/Handle AL 1.5,DL Orange w/Handle AL 1.5,DL Yellow w/Handle AL 2.0,DL Brown w/Handle ZN 2.0,DL MintGreen w/Handle ZN 2.0,DL Orange w/Handle ZN 2.0,DL Green w/Handle AL 2.0,DL Lavender w/Handle ZN 2.0,DL Brown w/Handle AL 1.5,DL Pink w/Handle AL 2.0,DL Yellow w/Handle ZN 2.0,DL Brown w/Handle AL 2.0,DL Lavender w/Handle AL 2.0</t>
+        </is>
+      </c>
+      <c r="D19" s="3">
         <v>165</v>
       </c>
-      <c r="D19" s="4">
+      <c r="E19" s="4">
         <v>3652.29</v>
       </c>
-      <c r="E19" s="3">
+      <c r="F19" s="3">
         <v>163</v>
       </c>
-      <c r="F19" s="3">
+      <c r="G19" s="3">
         <v>432</v>
       </c>
-      <c r="G19" s="3">
+      <c r="H19" s="3">
         <v>1915</v>
       </c>
-      <c r="H19" s="3">
+      <c r="I19" s="3">
         <v>2347</v>
       </c>
-      <c r="I19" s="3">
+      <c r="J19" s="3">
         <v>568</v>
       </c>
-      <c r="J19" s="3">
+      <c r="K19" s="3">
         <v>2383</v>
       </c>
-      <c r="K19" s="3">
+      <c r="L19" s="3">
         <v>2951</v>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>6.95%</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>27.91%</t>
         </is>
